--- a/Luban/Excel/日期.xlsx
+++ b/Luban/Excel/日期.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB1868C-B09B-41A3-8EF9-0C02B260E4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView minimized="1" xWindow="1080" yWindow="1080" windowWidth="35565" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,18 +35,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>think</author>
   </authors>
   <commentList>
-    <comment ref="G2" authorId="0">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>think:</t>
@@ -49,6 +56,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -1415,14 +1423,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1435,365 +1437,46 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1816,255 +1499,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2077,69 +1518,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2389,92 +1783,92 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K459"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="4" width="9" style="2"/>
-    <col min="5" max="6" width="23.1111111111111" style="2" customWidth="1"/>
+    <col min="5" max="6" width="23.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="52.5555555555556" style="2" customWidth="1"/>
+    <col min="8" max="8" width="52.5" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.2" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-    </row>
-    <row r="2" ht="16.2" spans="1:11">
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" ht="16.2" spans="1:11">
-      <c r="A3" s="5" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="2:7">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B4" s="2">
         <v>1706</v>
       </c>
@@ -2491,7 +1885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B5" s="2">
         <v>1706</v>
       </c>
@@ -2508,7 +1902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B6" s="2">
         <v>1706</v>
       </c>
@@ -2525,7 +1919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B7" s="2">
         <v>1706</v>
       </c>
@@ -2545,7 +1939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B8" s="2">
         <v>1706</v>
       </c>
@@ -2562,7 +1956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B9" s="2">
         <v>1706</v>
       </c>
@@ -2579,7 +1973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B10" s="2">
         <v>1706</v>
       </c>
@@ -2596,7 +1990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B11" s="2">
         <v>1706</v>
       </c>
@@ -2613,7 +2007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B12" s="2">
         <v>1706</v>
       </c>
@@ -2630,7 +2024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B13" s="2">
         <v>1706</v>
       </c>
@@ -2647,7 +2041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B14" s="2">
         <v>1706</v>
       </c>
@@ -2664,7 +2058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B15" s="2">
         <v>1706</v>
       </c>
@@ -2681,7 +2075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B16" s="2">
         <v>1706</v>
       </c>
@@ -2698,7 +2092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="2">
         <v>1706</v>
       </c>
@@ -2715,7 +2109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="2">
         <v>1706</v>
       </c>
@@ -2732,7 +2126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="2">
         <v>1706</v>
       </c>
@@ -2752,7 +2146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="2">
         <v>1706</v>
       </c>
@@ -2769,7 +2163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="2">
         <v>1706</v>
       </c>
@@ -2786,7 +2180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="2">
         <v>1706</v>
       </c>
@@ -2803,7 +2197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="2">
         <v>1706</v>
       </c>
@@ -2820,7 +2214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="2">
         <v>1706</v>
       </c>
@@ -2837,7 +2231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="2">
         <v>1706</v>
       </c>
@@ -2854,7 +2248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="2">
         <v>1706</v>
       </c>
@@ -2871,7 +2265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="2">
         <v>1706</v>
       </c>
@@ -2888,7 +2282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="2">
         <v>1706</v>
       </c>
@@ -2908,7 +2302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="2">
         <v>1706</v>
       </c>
@@ -2925,7 +2319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="2">
         <v>1706</v>
       </c>
@@ -2942,7 +2336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="2">
         <v>1706</v>
       </c>
@@ -2959,7 +2353,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="2">
         <v>1706</v>
       </c>
@@ -2976,7 +2370,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="2">
         <v>1706</v>
       </c>
@@ -2993,7 +2387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="2">
         <v>1706</v>
       </c>
@@ -3010,7 +2404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="2">
         <v>1706</v>
       </c>
@@ -3027,7 +2421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="2">
         <v>1706</v>
       </c>
@@ -3044,7 +2438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="2">
         <v>1706</v>
       </c>
@@ -3064,7 +2458,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="2">
         <v>1706</v>
       </c>
@@ -3081,7 +2475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:7">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="2">
         <v>1706</v>
       </c>
@@ -3098,7 +2492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="2">
         <v>1706</v>
       </c>
@@ -3115,7 +2509,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="2">
         <v>1706</v>
       </c>
@@ -3132,7 +2526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:7">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="2">
         <v>1706</v>
       </c>
@@ -3149,7 +2543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:7">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="2">
         <v>1706</v>
       </c>
@@ -3166,7 +2560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:7">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="2">
         <v>1706</v>
       </c>
@@ -3183,7 +2577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="2">
         <v>1706</v>
       </c>
@@ -3200,7 +2594,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="2">
         <v>1706</v>
       </c>
@@ -3217,7 +2611,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B47" s="2">
         <v>1706</v>
       </c>
@@ -3234,7 +2628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="2:7">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B48" s="2">
         <v>1706</v>
       </c>
@@ -3251,7 +2645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="2:8">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B49" s="2">
         <v>1706</v>
       </c>
@@ -3271,7 +2665,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B50" s="2">
         <v>1706</v>
       </c>
@@ -3288,7 +2682,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B51" s="2">
         <v>1706</v>
       </c>
@@ -3305,7 +2699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B52" s="2">
         <v>1706</v>
       </c>
@@ -3322,7 +2716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B53" s="2">
         <v>1706</v>
       </c>
@@ -3339,7 +2733,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="2:7">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B54" s="2">
         <v>1706</v>
       </c>
@@ -3356,7 +2750,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="2:7">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B55" s="2">
         <v>1706</v>
       </c>
@@ -3373,7 +2767,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="2:7">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B56" s="2">
         <v>1706</v>
       </c>
@@ -3390,7 +2784,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B57" s="2">
         <v>1706</v>
       </c>
@@ -3407,7 +2801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="2:8">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B58" s="2">
         <v>1706</v>
       </c>
@@ -3427,7 +2821,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="2:7">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B59" s="2">
         <v>1706</v>
       </c>
@@ -3444,7 +2838,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="2:7">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B60" s="2">
         <v>1706</v>
       </c>
@@ -3461,7 +2855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="2:7">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B61" s="2">
         <v>1706</v>
       </c>
@@ -3478,7 +2872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="2:7">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B62" s="2">
         <v>1706</v>
       </c>
@@ -3495,7 +2889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="2:7">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B63" s="2">
         <v>1706</v>
       </c>
@@ -3512,7 +2906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="2:7">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B64" s="2">
         <v>1706</v>
       </c>
@@ -3529,7 +2923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="2:7">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B65" s="2">
         <v>1706</v>
       </c>
@@ -3546,7 +2940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="2:7">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B66" s="2">
         <v>1706</v>
       </c>
@@ -3563,7 +2957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="2:8">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B67" s="2">
         <v>1706</v>
       </c>
@@ -3583,7 +2977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="2:7">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B68" s="2">
         <v>1706</v>
       </c>
@@ -3600,7 +2994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="2:7">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B69" s="2">
         <v>1706</v>
       </c>
@@ -3617,7 +3011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="2:7">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B70" s="2">
         <v>1706</v>
       </c>
@@ -3634,7 +3028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="2:7">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B71" s="2">
         <v>1706</v>
       </c>
@@ -3651,7 +3045,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="2:7">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B72" s="2">
         <v>1706</v>
       </c>
@@ -3668,7 +3062,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="2:7">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B73" s="2">
         <v>1706</v>
       </c>
@@ -3685,7 +3079,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="2:7">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B74" s="2">
         <v>1706</v>
       </c>
@@ -3702,7 +3096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="2:7">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B75" s="2">
         <v>1706</v>
       </c>
@@ -3719,7 +3113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="2:7">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B76" s="2">
         <v>1706</v>
       </c>
@@ -3736,7 +3130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="2:7">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B77" s="2">
         <v>1706</v>
       </c>
@@ -3753,7 +3147,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="2:7">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B78" s="2">
         <v>1706</v>
       </c>
@@ -3770,7 +3164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="2:8">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B79" s="2">
         <v>1706</v>
       </c>
@@ -3790,7 +3184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="2:7">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B80" s="2">
         <v>1706</v>
       </c>
@@ -3807,7 +3201,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="2:7">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="2">
         <v>1706</v>
       </c>
@@ -3824,7 +3218,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="2:7">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="2">
         <v>1706</v>
       </c>
@@ -3841,7 +3235,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="2:7">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="2">
         <v>1706</v>
       </c>
@@ -3858,7 +3252,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="2:7">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B84" s="2">
         <v>1707</v>
       </c>
@@ -3875,7 +3269,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="2:7">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="2">
         <v>1707</v>
       </c>
@@ -3892,7 +3286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="2:7">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="2">
         <v>1707</v>
       </c>
@@ -3909,7 +3303,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="2:8">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="2">
         <v>1707</v>
       </c>
@@ -3929,7 +3323,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="2:7">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="2">
         <v>1707</v>
       </c>
@@ -3946,7 +3340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="2:7">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="2">
         <v>1707</v>
       </c>
@@ -3963,7 +3357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="2:7">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="2">
         <v>1707</v>
       </c>
@@ -3980,7 +3374,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="2:7">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="2">
         <v>1707</v>
       </c>
@@ -3997,7 +3391,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="2:7">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="2">
         <v>1707</v>
       </c>
@@ -4014,7 +3408,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="2:7">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="2">
         <v>1707</v>
       </c>
@@ -4031,7 +3425,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="2:7">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B94" s="2">
         <v>1707</v>
       </c>
@@ -4048,7 +3442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="2:7">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="2">
         <v>1707</v>
       </c>
@@ -4065,7 +3459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="2">
         <v>1707</v>
       </c>
@@ -4085,7 +3479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="2:7">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="2">
         <v>1707</v>
       </c>
@@ -4102,7 +3496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="2:7">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="2">
         <v>1707</v>
       </c>
@@ -4119,7 +3513,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="2:7">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="2">
         <v>1707</v>
       </c>
@@ -4136,7 +3530,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="2:7">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="2">
         <v>1707</v>
       </c>
@@ -4153,7 +3547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="2:7">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="2">
         <v>1707</v>
       </c>
@@ -4170,7 +3564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="2:7">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="2">
         <v>1707</v>
       </c>
@@ -4187,7 +3581,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="2:7">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="2">
         <v>1707</v>
       </c>
@@ -4204,7 +3598,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="2:7">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="2">
         <v>1707</v>
       </c>
@@ -4221,7 +3615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="2:7">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="2">
         <v>1707</v>
       </c>
@@ -4238,7 +3632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="2:7">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="2">
         <v>1707</v>
       </c>
@@ -4255,7 +3649,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="2:7">
+    <row r="107" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B107" s="2">
         <v>1707</v>
       </c>
@@ -4272,7 +3666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="2:8">
+    <row r="108" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B108" s="2">
         <v>1707</v>
       </c>
@@ -4292,7 +3686,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="2:7">
+    <row r="109" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B109" s="2">
         <v>1707</v>
       </c>
@@ -4309,7 +3703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="2:7">
+    <row r="110" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B110" s="2">
         <v>1707</v>
       </c>
@@ -4326,7 +3720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="2:7">
+    <row r="111" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B111" s="2">
         <v>1707</v>
       </c>
@@ -4343,7 +3737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="2:7">
+    <row r="112" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B112" s="2">
         <v>1707</v>
       </c>
@@ -4360,7 +3754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="2:7">
+    <row r="113" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B113" s="2">
         <v>1707</v>
       </c>
@@ -4377,7 +3771,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="2:7">
+    <row r="114" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B114" s="2">
         <v>1707</v>
       </c>
@@ -4394,7 +3788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="2:7">
+    <row r="115" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B115" s="2">
         <v>1707</v>
       </c>
@@ -4411,7 +3805,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="2:7">
+    <row r="116" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B116" s="2">
         <v>1707</v>
       </c>
@@ -4428,7 +3822,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="2:8">
+    <row r="117" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B117" s="2">
         <v>1707</v>
       </c>
@@ -4448,7 +3842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="2:7">
+    <row r="118" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B118" s="2">
         <v>1707</v>
       </c>
@@ -4465,7 +3859,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="2:7">
+    <row r="119" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B119" s="2">
         <v>1707</v>
       </c>
@@ -4482,7 +3876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="2:7">
+    <row r="120" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B120" s="2">
         <v>1707</v>
       </c>
@@ -4499,7 +3893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="2:7">
+    <row r="121" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B121" s="2">
         <v>1707</v>
       </c>
@@ -4516,7 +3910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="2:7">
+    <row r="122" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B122" s="2">
         <v>1707</v>
       </c>
@@ -4533,7 +3927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="2:7">
+    <row r="123" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B123" s="2">
         <v>1707</v>
       </c>
@@ -4550,7 +3944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="2:7">
+    <row r="124" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B124" s="2">
         <v>1707</v>
       </c>
@@ -4567,7 +3961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="2:7">
+    <row r="125" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B125" s="2">
         <v>1707</v>
       </c>
@@ -4584,7 +3978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="2:8">
+    <row r="126" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B126" s="2">
         <v>1707</v>
       </c>
@@ -4604,7 +3998,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="2:7">
+    <row r="127" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B127" s="2">
         <v>1707</v>
       </c>
@@ -4621,7 +4015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="2:7">
+    <row r="128" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B128" s="2">
         <v>1707</v>
       </c>
@@ -4638,7 +4032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="2:7">
+    <row r="129" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B129" s="2">
         <v>1707</v>
       </c>
@@ -4655,7 +4049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="2:7">
+    <row r="130" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B130" s="2">
         <v>1707</v>
       </c>
@@ -4672,7 +4066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="2:7">
+    <row r="131" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B131" s="2">
         <v>1707</v>
       </c>
@@ -4689,7 +4083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="2:7">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B132" s="2">
         <v>1707</v>
       </c>
@@ -4706,7 +4100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="2:7">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B133" s="2">
         <v>1707</v>
       </c>
@@ -4723,7 +4117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="2:7">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B134" s="2">
         <v>1707</v>
       </c>
@@ -4740,7 +4134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="2:7">
+    <row r="135" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B135" s="2">
         <v>1707</v>
       </c>
@@ -4757,7 +4151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="2:7">
+    <row r="136" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B136" s="2">
         <v>1707</v>
       </c>
@@ -4774,7 +4168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="2:7">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B137" s="2">
         <v>1707</v>
       </c>
@@ -4791,7 +4185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="2:8">
+    <row r="138" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B138" s="2">
         <v>1707</v>
       </c>
@@ -4811,7 +4205,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="2:7">
+    <row r="139" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B139" s="2">
         <v>1707</v>
       </c>
@@ -4828,7 +4222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="2:7">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B140" s="2">
         <v>1707</v>
       </c>
@@ -4845,7 +4239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="2:7">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B141" s="2">
         <v>1707</v>
       </c>
@@ -4862,7 +4256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="2:7">
+    <row r="142" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B142" s="2">
         <v>1707</v>
       </c>
@@ -4879,7 +4273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="2:7">
+    <row r="143" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B143" s="2">
         <v>1707</v>
       </c>
@@ -4896,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="2:7">
+    <row r="144" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B144" s="2">
         <v>1707</v>
       </c>
@@ -4913,7 +4307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="2:7">
+    <row r="145" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B145" s="2">
         <v>1707</v>
       </c>
@@ -4930,7 +4324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="2:8">
+    <row r="146" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B146" s="2">
         <v>1707</v>
       </c>
@@ -4950,7 +4344,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="2:7">
+    <row r="147" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B147" s="2">
         <v>1707</v>
       </c>
@@ -4967,7 +4361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="2:7">
+    <row r="148" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B148" s="2">
         <v>1707</v>
       </c>
@@ -4984,7 +4378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="2:7">
+    <row r="149" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B149" s="2">
         <v>1707</v>
       </c>
@@ -5001,7 +4395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="2:7">
+    <row r="150" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B150" s="2">
         <v>1707</v>
       </c>
@@ -5018,7 +4412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="2:7">
+    <row r="151" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B151" s="2">
         <v>1707</v>
       </c>
@@ -5035,7 +4429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="2:7">
+    <row r="152" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B152" s="2">
         <v>1707</v>
       </c>
@@ -5052,7 +4446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="2:7">
+    <row r="153" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B153" s="2">
         <v>1707</v>
       </c>
@@ -5069,7 +4463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="2:7">
+    <row r="154" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B154" s="2">
         <v>1707</v>
       </c>
@@ -5086,7 +4480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="2:8">
+    <row r="155" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B155" s="2">
         <v>1707</v>
       </c>
@@ -5106,7 +4500,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="2:7">
+    <row r="156" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B156" s="2">
         <v>1707</v>
       </c>
@@ -5123,7 +4517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="2:7">
+    <row r="157" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B157" s="2">
         <v>1707</v>
       </c>
@@ -5140,7 +4534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="2:7">
+    <row r="158" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B158" s="2">
         <v>1707</v>
       </c>
@@ -5157,7 +4551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="2:7">
+    <row r="159" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B159" s="2">
         <v>1707</v>
       </c>
@@ -5174,7 +4568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="2:7">
+    <row r="160" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B160" s="2">
         <v>1707</v>
       </c>
@@ -5191,7 +4585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="2:7">
+    <row r="161" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B161" s="2">
         <v>1707</v>
       </c>
@@ -5208,7 +4602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="2:7">
+    <row r="162" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B162" s="2">
         <v>1707</v>
       </c>
@@ -5225,7 +4619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="2:7">
+    <row r="163" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B163" s="2">
         <v>1707</v>
       </c>
@@ -5242,7 +4636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="2:7">
+    <row r="164" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B164" s="2">
         <v>1707</v>
       </c>
@@ -5259,7 +4653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="2:7">
+    <row r="165" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B165" s="2">
         <v>1707</v>
       </c>
@@ -5276,7 +4670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="2:7">
+    <row r="166" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B166" s="2">
         <v>1707</v>
       </c>
@@ -5293,7 +4687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="2:8">
+    <row r="167" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B167" s="2">
         <v>1707</v>
       </c>
@@ -5313,7 +4707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="2:7">
+    <row r="168" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B168" s="2">
         <v>1707</v>
       </c>
@@ -5330,7 +4724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="2:7">
+    <row r="169" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B169" s="2">
         <v>1707</v>
       </c>
@@ -5347,7 +4741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="2:7">
+    <row r="170" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B170" s="2">
         <v>1707</v>
       </c>
@@ -5364,7 +4758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="2:7">
+    <row r="171" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B171" s="2">
         <v>1707</v>
       </c>
@@ -5381,7 +4775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="2:7">
+    <row r="172" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B172" s="2">
         <v>1707</v>
       </c>
@@ -5398,7 +4792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="2:7">
+    <row r="173" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B173" s="2">
         <v>1707</v>
       </c>
@@ -5415,7 +4809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="2:7">
+    <row r="174" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B174" s="2">
         <v>1707</v>
       </c>
@@ -5432,7 +4826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="2:8">
+    <row r="175" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B175" s="2">
         <v>1707</v>
       </c>
@@ -5452,7 +4846,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="2:7">
+    <row r="176" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B176" s="2">
         <v>1707</v>
       </c>
@@ -5469,7 +4863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="2:7">
+    <row r="177" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B177" s="2">
         <v>1707</v>
       </c>
@@ -5486,7 +4880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="2:7">
+    <row r="178" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B178" s="2">
         <v>1707</v>
       </c>
@@ -5503,7 +4897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="2:7">
+    <row r="179" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B179" s="2">
         <v>1707</v>
       </c>
@@ -5520,7 +4914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="2:7">
+    <row r="180" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B180" s="2">
         <v>1707</v>
       </c>
@@ -5537,7 +4931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="2:7">
+    <row r="181" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B181" s="2">
         <v>1707</v>
       </c>
@@ -5554,7 +4948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="2:7">
+    <row r="182" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B182" s="2">
         <v>1707</v>
       </c>
@@ -5571,7 +4965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="2:7">
+    <row r="183" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B183" s="2">
         <v>1707</v>
       </c>
@@ -5588,7 +4982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="2:8">
+    <row r="184" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B184" s="2">
         <v>1707</v>
       </c>
@@ -5608,7 +5002,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="185" spans="2:7">
+    <row r="185" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B185" s="2">
         <v>1707</v>
       </c>
@@ -5625,7 +5019,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="2:7">
+    <row r="186" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B186" s="2">
         <v>1707</v>
       </c>
@@ -5642,7 +5036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="2:7">
+    <row r="187" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B187" s="2">
         <v>1707</v>
       </c>
@@ -5659,7 +5053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="2:7">
+    <row r="188" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B188" s="2">
         <v>1707</v>
       </c>
@@ -5676,7 +5070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="2:7">
+    <row r="189" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B189" s="2">
         <v>1707</v>
       </c>
@@ -5693,7 +5087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="2:7">
+    <row r="190" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B190" s="2">
         <v>1707</v>
       </c>
@@ -5710,7 +5104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="2:7">
+    <row r="191" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B191" s="2">
         <v>1707</v>
       </c>
@@ -5727,7 +5121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="2:7">
+    <row r="192" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B192" s="2">
         <v>1707</v>
       </c>
@@ -5744,7 +5138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="2:7">
+    <row r="193" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B193" s="2">
         <v>1707</v>
       </c>
@@ -5761,7 +5155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="2:7">
+    <row r="194" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B194" s="2">
         <v>1707</v>
       </c>
@@ -5778,7 +5172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="2:7">
+    <row r="195" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B195" s="2">
         <v>1707</v>
       </c>
@@ -5795,7 +5189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="2:8">
+    <row r="196" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B196" s="2">
         <v>1707</v>
       </c>
@@ -5815,7 +5209,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="2:7">
+    <row r="197" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B197" s="2">
         <v>1707</v>
       </c>
@@ -5832,7 +5226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="2:7">
+    <row r="198" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B198" s="2">
         <v>1707</v>
       </c>
@@ -5849,7 +5243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="2:7">
+    <row r="199" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B199" s="2">
         <v>1707</v>
       </c>
@@ -5866,7 +5260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="2:7">
+    <row r="200" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B200" s="2">
         <v>1707</v>
       </c>
@@ -5883,7 +5277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="2:7">
+    <row r="201" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B201" s="2">
         <v>1707</v>
       </c>
@@ -5900,7 +5294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="2:7">
+    <row r="202" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B202" s="2">
         <v>1707</v>
       </c>
@@ -5917,7 +5311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="2:7">
+    <row r="203" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B203" s="2">
         <v>1707</v>
       </c>
@@ -5934,7 +5328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="2:7">
+    <row r="204" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B204" s="2">
         <v>1707</v>
       </c>
@@ -5951,7 +5345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="2:7">
+    <row r="205" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B205" s="2">
         <v>1707</v>
       </c>
@@ -5968,7 +5362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="2:8">
+    <row r="206" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B206" s="2">
         <v>1707</v>
       </c>
@@ -5988,7 +5382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="2:7">
+    <row r="207" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B207" s="2">
         <v>1707</v>
       </c>
@@ -6005,7 +5399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="2:7">
+    <row r="208" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B208" s="2">
         <v>1707</v>
       </c>
@@ -6022,7 +5416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="2:7">
+    <row r="209" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B209" s="2">
         <v>1707</v>
       </c>
@@ -6039,7 +5433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="2:7">
+    <row r="210" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B210" s="2">
         <v>1707</v>
       </c>
@@ -6056,7 +5450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="2:7">
+    <row r="211" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B211" s="2">
         <v>1707</v>
       </c>
@@ -6073,7 +5467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="2:7">
+    <row r="212" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B212" s="2">
         <v>1707</v>
       </c>
@@ -6090,7 +5484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="2:7">
+    <row r="213" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B213" s="2">
         <v>1707</v>
       </c>
@@ -6107,7 +5501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="2:8">
+    <row r="214" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B214" s="2">
         <v>1707</v>
       </c>
@@ -6127,7 +5521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" spans="2:7">
+    <row r="215" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B215" s="2">
         <v>1707</v>
       </c>
@@ -6144,7 +5538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="2:7">
+    <row r="216" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B216" s="2">
         <v>1707</v>
       </c>
@@ -6161,7 +5555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="2:7">
+    <row r="217" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B217" s="2">
         <v>1707</v>
       </c>
@@ -6178,7 +5572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="2:7">
+    <row r="218" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B218" s="2">
         <v>1707</v>
       </c>
@@ -6195,7 +5589,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="2:7">
+    <row r="219" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B219" s="2">
         <v>1707</v>
       </c>
@@ -6212,7 +5606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="2:7">
+    <row r="220" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B220" s="2">
         <v>1707</v>
       </c>
@@ -6229,7 +5623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="2:7">
+    <row r="221" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B221" s="2">
         <v>1707</v>
       </c>
@@ -6246,7 +5640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="2:7">
+    <row r="222" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B222" s="2">
         <v>1707</v>
       </c>
@@ -6263,7 +5657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="2:8">
+    <row r="223" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B223" s="2">
         <v>1707</v>
       </c>
@@ -6283,7 +5677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="224" spans="2:7">
+    <row r="224" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B224" s="2">
         <v>1707</v>
       </c>
@@ -6300,7 +5694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="2:7">
+    <row r="225" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B225" s="2">
         <v>1707</v>
       </c>
@@ -6317,7 +5711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="2:7">
+    <row r="226" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B226" s="2">
         <v>1707</v>
       </c>
@@ -6334,7 +5728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="2:7">
+    <row r="227" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B227" s="2">
         <v>1707</v>
       </c>
@@ -6351,7 +5745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="2:7">
+    <row r="228" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B228" s="2">
         <v>1707</v>
       </c>
@@ -6368,7 +5762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="2:7">
+    <row r="229" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B229" s="2">
         <v>1707</v>
       </c>
@@ -6385,7 +5779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="2:7">
+    <row r="230" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B230" s="2">
         <v>1707</v>
       </c>
@@ -6402,7 +5796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="2:7">
+    <row r="231" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B231" s="2">
         <v>1707</v>
       </c>
@@ -6419,7 +5813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="2:7">
+    <row r="232" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B232" s="2">
         <v>1707</v>
       </c>
@@ -6436,7 +5830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="2:7">
+    <row r="233" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B233" s="2">
         <v>1707</v>
       </c>
@@ -6453,7 +5847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="2:7">
+    <row r="234" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B234" s="2">
         <v>1707</v>
       </c>
@@ -6470,7 +5864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="2:8">
+    <row r="235" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B235" s="2">
         <v>1707</v>
       </c>
@@ -6490,7 +5884,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" spans="2:7">
+    <row r="236" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B236" s="2">
         <v>1707</v>
       </c>
@@ -6507,7 +5901,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="2:7">
+    <row r="237" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B237" s="2">
         <v>1707</v>
       </c>
@@ -6524,7 +5918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="2:7">
+    <row r="238" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B238" s="2">
         <v>1707</v>
       </c>
@@ -6541,7 +5935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="2:7">
+    <row r="239" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B239" s="2">
         <v>1707</v>
       </c>
@@ -6558,7 +5952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="2:7">
+    <row r="240" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B240" s="2">
         <v>1707</v>
       </c>
@@ -6575,7 +5969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="2:7">
+    <row r="241" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B241" s="2">
         <v>1707</v>
       </c>
@@ -6592,7 +5986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="2:7">
+    <row r="242" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B242" s="2">
         <v>1707</v>
       </c>
@@ -6609,7 +6003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="2:7">
+    <row r="243" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B243" s="2">
         <v>1707</v>
       </c>
@@ -6626,7 +6020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="2:8">
+    <row r="244" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B244" s="2">
         <v>1707</v>
       </c>
@@ -6646,7 +6040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" spans="2:7">
+    <row r="245" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B245" s="2">
         <v>1707</v>
       </c>
@@ -6663,7 +6057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="2:7">
+    <row r="246" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B246" s="2">
         <v>1707</v>
       </c>
@@ -6680,7 +6074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="2:7">
+    <row r="247" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B247" s="2">
         <v>1707</v>
       </c>
@@ -6697,7 +6091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="2:7">
+    <row r="248" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B248" s="2">
         <v>1707</v>
       </c>
@@ -6714,7 +6108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="2:7">
+    <row r="249" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B249" s="2">
         <v>1707</v>
       </c>
@@ -6731,7 +6125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="2:7">
+    <row r="250" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B250" s="2">
         <v>1707</v>
       </c>
@@ -6748,7 +6142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="2:7">
+    <row r="251" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B251" s="2">
         <v>1707</v>
       </c>
@@ -6765,7 +6159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="2:8">
+    <row r="252" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B252" s="2">
         <v>1707</v>
       </c>
@@ -6785,7 +6179,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="253" spans="2:7">
+    <row r="253" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B253" s="2">
         <v>1707</v>
       </c>
@@ -6802,7 +6196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="2:7">
+    <row r="254" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B254" s="2">
         <v>1707</v>
       </c>
@@ -6819,7 +6213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="2:7">
+    <row r="255" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B255" s="2">
         <v>1707</v>
       </c>
@@ -6836,7 +6230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="2:7">
+    <row r="256" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B256" s="2">
         <v>1707</v>
       </c>
@@ -6853,7 +6247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="257" spans="2:7">
+    <row r="257" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B257" s="2">
         <v>1707</v>
       </c>
@@ -6870,7 +6264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="2:7">
+    <row r="258" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B258" s="2">
         <v>1707</v>
       </c>
@@ -6887,7 +6281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="2:7">
+    <row r="259" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B259" s="2">
         <v>1707</v>
       </c>
@@ -6904,7 +6298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="260" spans="2:7">
+    <row r="260" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B260" s="2">
         <v>1707</v>
       </c>
@@ -6921,7 +6315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="2:8">
+    <row r="261" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B261" s="2">
         <v>1707</v>
       </c>
@@ -6941,7 +6335,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="262" spans="2:7">
+    <row r="262" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B262" s="2">
         <v>1707</v>
       </c>
@@ -6958,7 +6352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="2:7">
+    <row r="263" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B263" s="2">
         <v>1707</v>
       </c>
@@ -6975,7 +6369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="2:7">
+    <row r="264" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B264" s="2">
         <v>1707</v>
       </c>
@@ -6992,7 +6386,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="2:7">
+    <row r="265" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B265" s="2">
         <v>1707</v>
       </c>
@@ -7009,7 +6403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="2:7">
+    <row r="266" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B266" s="2">
         <v>1707</v>
       </c>
@@ -7026,7 +6420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="2:7">
+    <row r="267" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B267" s="2">
         <v>1707</v>
       </c>
@@ -7043,7 +6437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="268" spans="2:7">
+    <row r="268" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B268" s="2">
         <v>1707</v>
       </c>
@@ -7060,7 +6454,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="2:7">
+    <row r="269" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B269" s="2">
         <v>1707</v>
       </c>
@@ -7077,7 +6471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="2:7">
+    <row r="270" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B270" s="2">
         <v>1707</v>
       </c>
@@ -7094,7 +6488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="271" spans="2:7">
+    <row r="271" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B271" s="2">
         <v>1707</v>
       </c>
@@ -7111,7 +6505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="272" spans="2:7">
+    <row r="272" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B272" s="2">
         <v>1707</v>
       </c>
@@ -7128,7 +6522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="273" spans="2:8">
+    <row r="273" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B273" s="2">
         <v>1707</v>
       </c>
@@ -7148,7 +6542,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="274" spans="2:7">
+    <row r="274" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B274" s="2">
         <v>1707</v>
       </c>
@@ -7165,7 +6559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="275" spans="2:7">
+    <row r="275" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B275" s="2">
         <v>1707</v>
       </c>
@@ -7182,7 +6576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="276" spans="2:7">
+    <row r="276" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B276" s="2">
         <v>1707</v>
       </c>
@@ -7199,7 +6593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="277" spans="2:7">
+    <row r="277" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B277" s="2">
         <v>1707</v>
       </c>
@@ -7216,7 +6610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="2:7">
+    <row r="278" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B278" s="2">
         <v>1707</v>
       </c>
@@ -7233,7 +6627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="279" spans="2:7">
+    <row r="279" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B279" s="2">
         <v>1707</v>
       </c>
@@ -7250,7 +6644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="2:7">
+    <row r="280" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B280" s="2">
         <v>1707</v>
       </c>
@@ -7267,7 +6661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="2:8">
+    <row r="281" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B281" s="2">
         <v>1707</v>
       </c>
@@ -7287,7 +6681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="282" spans="2:7">
+    <row r="282" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B282" s="2">
         <v>1707</v>
       </c>
@@ -7304,7 +6698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="283" spans="2:7">
+    <row r="283" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B283" s="2">
         <v>1707</v>
       </c>
@@ -7321,7 +6715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="284" spans="2:7">
+    <row r="284" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B284" s="2">
         <v>1707</v>
       </c>
@@ -7338,7 +6732,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="2:7">
+    <row r="285" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B285" s="2">
         <v>1707</v>
       </c>
@@ -7355,7 +6749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="2:7">
+    <row r="286" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B286" s="2">
         <v>1707</v>
       </c>
@@ -7372,7 +6766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="2:7">
+    <row r="287" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B287" s="2">
         <v>1707</v>
       </c>
@@ -7389,7 +6783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="288" spans="2:7">
+    <row r="288" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B288" s="2">
         <v>1707</v>
       </c>
@@ -7406,7 +6800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="2:7">
+    <row r="289" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B289" s="2">
         <v>1707</v>
       </c>
@@ -7423,7 +6817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="290" spans="2:8">
+    <row r="290" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B290" s="2">
         <v>1707</v>
       </c>
@@ -7443,7 +6837,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="291" spans="2:7">
+    <row r="291" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B291" s="2">
         <v>1707</v>
       </c>
@@ -7460,7 +6854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="292" spans="2:7">
+    <row r="292" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B292" s="2">
         <v>1707</v>
       </c>
@@ -7477,7 +6871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="2:7">
+    <row r="293" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B293" s="2">
         <v>1707</v>
       </c>
@@ -7494,7 +6888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="2:7">
+    <row r="294" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B294" s="2">
         <v>1707</v>
       </c>
@@ -7511,7 +6905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="295" spans="2:7">
+    <row r="295" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B295" s="2">
         <v>1707</v>
       </c>
@@ -7528,7 +6922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="2:7">
+    <row r="296" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B296" s="2">
         <v>1707</v>
       </c>
@@ -7545,7 +6939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="2:7">
+    <row r="297" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B297" s="2">
         <v>1707</v>
       </c>
@@ -7562,7 +6956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="2:7">
+    <row r="298" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B298" s="2">
         <v>1707</v>
       </c>
@@ -7579,7 +6973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="2:7">
+    <row r="299" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B299" s="2">
         <v>1707</v>
       </c>
@@ -7596,7 +6990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="2:7">
+    <row r="300" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B300" s="2">
         <v>1707</v>
       </c>
@@ -7613,7 +7007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="2:7">
+    <row r="301" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B301" s="2">
         <v>1707</v>
       </c>
@@ -7630,7 +7024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="2:8">
+    <row r="302" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B302" s="2">
         <v>1707</v>
       </c>
@@ -7650,7 +7044,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="303" spans="2:7">
+    <row r="303" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B303" s="2">
         <v>1707</v>
       </c>
@@ -7667,7 +7061,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="2:7">
+    <row r="304" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B304" s="2">
         <v>1707</v>
       </c>
@@ -7684,7 +7078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="305" spans="2:7">
+    <row r="305" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B305" s="2">
         <v>1707</v>
       </c>
@@ -7701,7 +7095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="2:7">
+    <row r="306" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B306" s="2">
         <v>1707</v>
       </c>
@@ -7718,7 +7112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="2:7">
+    <row r="307" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B307" s="2">
         <v>1707</v>
       </c>
@@ -7735,7 +7129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="2:7">
+    <row r="308" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B308" s="2">
         <v>1707</v>
       </c>
@@ -7752,7 +7146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="2:7">
+    <row r="309" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B309" s="2">
         <v>1707</v>
       </c>
@@ -7769,7 +7163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="2:7">
+    <row r="310" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B310" s="2">
         <v>1707</v>
       </c>
@@ -7786,7 +7180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="2:8">
+    <row r="311" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B311" s="2">
         <v>1707</v>
       </c>
@@ -7806,7 +7200,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="312" spans="2:7">
+    <row r="312" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B312" s="2">
         <v>1707</v>
       </c>
@@ -7823,7 +7217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313" spans="2:7">
+    <row r="313" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B313" s="2">
         <v>1707</v>
       </c>
@@ -7840,7 +7234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="314" spans="2:7">
+    <row r="314" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B314" s="2">
         <v>1707</v>
       </c>
@@ -7857,7 +7251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="2:7">
+    <row r="315" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B315" s="2">
         <v>1707</v>
       </c>
@@ -7874,7 +7268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="316" spans="2:7">
+    <row r="316" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B316" s="2">
         <v>1707</v>
       </c>
@@ -7891,7 +7285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="2:7">
+    <row r="317" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B317" s="2">
         <v>1707</v>
       </c>
@@ -7908,7 +7302,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="2:7">
+    <row r="318" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B318" s="2">
         <v>1707</v>
       </c>
@@ -7925,7 +7319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="2:7">
+    <row r="319" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B319" s="2">
         <v>1707</v>
       </c>
@@ -7942,7 +7336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="2:8">
+    <row r="320" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B320" s="2">
         <v>1707</v>
       </c>
@@ -7962,7 +7356,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="321" spans="2:7">
+    <row r="321" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B321" s="2">
         <v>1707</v>
       </c>
@@ -7979,7 +7373,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="2:7">
+    <row r="322" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B322" s="2">
         <v>1707</v>
       </c>
@@ -7996,7 +7390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="2:7">
+    <row r="323" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B323" s="2">
         <v>1707</v>
       </c>
@@ -8013,7 +7407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="2:7">
+    <row r="324" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B324" s="2">
         <v>1707</v>
       </c>
@@ -8030,7 +7424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="2:7">
+    <row r="325" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B325" s="2">
         <v>1707</v>
       </c>
@@ -8047,7 +7441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="2:7">
+    <row r="326" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B326" s="2">
         <v>1707</v>
       </c>
@@ -8064,7 +7458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="2:7">
+    <row r="327" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B327" s="2">
         <v>1707</v>
       </c>
@@ -8081,7 +7475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="2:7">
+    <row r="328" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B328" s="2">
         <v>1707</v>
       </c>
@@ -8098,7 +7492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="2:7">
+    <row r="329" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B329" s="2">
         <v>1707</v>
       </c>
@@ -8115,7 +7509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="2:7">
+    <row r="330" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B330" s="2">
         <v>1707</v>
       </c>
@@ -8132,7 +7526,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="2:7">
+    <row r="331" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B331" s="2">
         <v>1707</v>
       </c>
@@ -8149,7 +7543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="2:8">
+    <row r="332" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B332" s="2">
         <v>1707</v>
       </c>
@@ -8169,7 +7563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="333" spans="2:7">
+    <row r="333" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B333" s="2">
         <v>1707</v>
       </c>
@@ -8186,7 +7580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="2:7">
+    <row r="334" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B334" s="2">
         <v>1707</v>
       </c>
@@ -8203,7 +7597,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="2:7">
+    <row r="335" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B335" s="2">
         <v>1707</v>
       </c>
@@ -8220,7 +7614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="2:7">
+    <row r="336" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B336" s="2">
         <v>1707</v>
       </c>
@@ -8237,7 +7631,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="2:7">
+    <row r="337" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B337" s="2">
         <v>1707</v>
       </c>
@@ -8254,7 +7648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="2:7">
+    <row r="338" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B338" s="2">
         <v>1707</v>
       </c>
@@ -8271,7 +7665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="2:7">
+    <row r="339" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B339" s="2">
         <v>1707</v>
       </c>
@@ -8288,7 +7682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="2:7">
+    <row r="340" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B340" s="2">
         <v>1707</v>
       </c>
@@ -8305,7 +7699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="2:8">
+    <row r="341" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B341" s="2">
         <v>1707</v>
       </c>
@@ -8325,7 +7719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="342" spans="2:7">
+    <row r="342" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B342" s="2">
         <v>1707</v>
       </c>
@@ -8342,7 +7736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="2:7">
+    <row r="343" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B343" s="2">
         <v>1707</v>
       </c>
@@ -8359,7 +7753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="2:7">
+    <row r="344" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B344" s="2">
         <v>1707</v>
       </c>
@@ -8376,7 +7770,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="2:7">
+    <row r="345" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B345" s="2">
         <v>1707</v>
       </c>
@@ -8393,7 +7787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="2:7">
+    <row r="346" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B346" s="2">
         <v>1707</v>
       </c>
@@ -8410,7 +7804,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="347" spans="2:7">
+    <row r="347" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B347" s="2">
         <v>1707</v>
       </c>
@@ -8427,7 +7821,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="2:7">
+    <row r="348" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B348" s="2">
         <v>1707</v>
       </c>
@@ -8444,7 +7838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="349" spans="2:7">
+    <row r="349" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B349" s="2">
         <v>1707</v>
       </c>
@@ -8461,7 +7855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="2:8">
+    <row r="350" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B350" s="2">
         <v>1707</v>
       </c>
@@ -8481,7 +7875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="351" spans="2:7">
+    <row r="351" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B351" s="2">
         <v>1707</v>
       </c>
@@ -8498,7 +7892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="352" spans="2:7">
+    <row r="352" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B352" s="2">
         <v>1707</v>
       </c>
@@ -8515,7 +7909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="2:7">
+    <row r="353" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B353" s="2">
         <v>1707</v>
       </c>
@@ -8532,7 +7926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="2:7">
+    <row r="354" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B354" s="2">
         <v>1707</v>
       </c>
@@ -8549,7 +7943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="2:7">
+    <row r="355" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B355" s="2">
         <v>1707</v>
       </c>
@@ -8566,7 +7960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="356" spans="2:7">
+    <row r="356" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B356" s="2">
         <v>1707</v>
       </c>
@@ -8583,7 +7977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="2:7">
+    <row r="357" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B357" s="2">
         <v>1707</v>
       </c>
@@ -8600,7 +7994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="358" spans="2:7">
+    <row r="358" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B358" s="2">
         <v>1707</v>
       </c>
@@ -8617,7 +8011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="359" spans="2:7">
+    <row r="359" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B359" s="2">
         <v>1707</v>
       </c>
@@ -8634,7 +8028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="360" spans="2:7">
+    <row r="360" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B360" s="2">
         <v>1707</v>
       </c>
@@ -8651,7 +8045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="2:7">
+    <row r="361" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B361" s="2">
         <v>1707</v>
       </c>
@@ -8668,7 +8062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="2:8">
+    <row r="362" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B362" s="2">
         <v>1707</v>
       </c>
@@ -8688,7 +8082,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="363" spans="2:7">
+    <row r="363" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B363" s="2">
         <v>1707</v>
       </c>
@@ -8705,7 +8099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="2:7">
+    <row r="364" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B364" s="2">
         <v>1707</v>
       </c>
@@ -8722,7 +8116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="2:7">
+    <row r="365" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B365" s="2">
         <v>1707</v>
       </c>
@@ -8739,7 +8133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="2:7">
+    <row r="366" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B366" s="2">
         <v>1707</v>
       </c>
@@ -8756,7 +8150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="2:7">
+    <row r="367" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B367" s="2">
         <v>1707</v>
       </c>
@@ -8773,7 +8167,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="2:7">
+    <row r="368" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B368" s="2">
         <v>1707</v>
       </c>
@@ -8790,7 +8184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="2:7">
+    <row r="369" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B369" s="2">
         <v>1707</v>
       </c>
@@ -8807,7 +8201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="2:8">
+    <row r="370" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B370" s="2">
         <v>1707</v>
       </c>
@@ -8827,7 +8221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="371" spans="2:7">
+    <row r="371" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B371" s="2">
         <v>1707</v>
       </c>
@@ -8844,7 +8238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="2:7">
+    <row r="372" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B372" s="2">
         <v>1707</v>
       </c>
@@ -8861,7 +8255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="2:7">
+    <row r="373" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B373" s="2">
         <v>1707</v>
       </c>
@@ -8878,7 +8272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="2:7">
+    <row r="374" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B374" s="2">
         <v>1707</v>
       </c>
@@ -8895,7 +8289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="2:7">
+    <row r="375" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B375" s="2">
         <v>1707</v>
       </c>
@@ -8912,7 +8306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="2:7">
+    <row r="376" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B376" s="2">
         <v>1707</v>
       </c>
@@ -8929,7 +8323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="2:7">
+    <row r="377" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B377" s="2">
         <v>1707</v>
       </c>
@@ -8946,7 +8340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="2:7">
+    <row r="378" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B378" s="2">
         <v>1707</v>
       </c>
@@ -8963,7 +8357,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="2:8">
+    <row r="379" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B379" s="2">
         <v>1707</v>
       </c>
@@ -8983,7 +8377,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="380" spans="2:7">
+    <row r="380" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B380" s="2">
         <v>1707</v>
       </c>
@@ -9000,7 +8394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="2:7">
+    <row r="381" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B381" s="2">
         <v>1707</v>
       </c>
@@ -9017,7 +8411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="2:7">
+    <row r="382" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B382" s="2">
         <v>1707</v>
       </c>
@@ -9034,7 +8428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="2:7">
+    <row r="383" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B383" s="2">
         <v>1707</v>
       </c>
@@ -9051,7 +8445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="2:7">
+    <row r="384" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B384" s="2">
         <v>1707</v>
       </c>
@@ -9068,7 +8462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="2:7">
+    <row r="385" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B385" s="2">
         <v>1707</v>
       </c>
@@ -9085,7 +8479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="2:7">
+    <row r="386" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B386" s="2">
         <v>1707</v>
       </c>
@@ -9102,7 +8496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="2:7">
+    <row r="387" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B387" s="2">
         <v>1707</v>
       </c>
@@ -9119,7 +8513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="2:7">
+    <row r="388" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B388" s="2">
         <v>1707</v>
       </c>
@@ -9136,7 +8530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="2:7">
+    <row r="389" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B389" s="2">
         <v>1707</v>
       </c>
@@ -9153,7 +8547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="2:7">
+    <row r="390" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B390" s="2">
         <v>1707</v>
       </c>
@@ -9170,7 +8564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="391" spans="2:8">
+    <row r="391" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B391" s="2">
         <v>1707</v>
       </c>
@@ -9190,7 +8584,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="392" spans="2:7">
+    <row r="392" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B392" s="2">
         <v>1707</v>
       </c>
@@ -9207,7 +8601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="393" spans="2:7">
+    <row r="393" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B393" s="2">
         <v>1707</v>
       </c>
@@ -9224,7 +8618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="394" spans="2:7">
+    <row r="394" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B394" s="2">
         <v>1707</v>
       </c>
@@ -9241,7 +8635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="395" spans="2:7">
+    <row r="395" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B395" s="2">
         <v>1707</v>
       </c>
@@ -9258,7 +8652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="396" spans="2:7">
+    <row r="396" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B396" s="2">
         <v>1707</v>
       </c>
@@ -9275,7 +8669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="397" spans="2:7">
+    <row r="397" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B397" s="2">
         <v>1707</v>
       </c>
@@ -9292,7 +8686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="2:7">
+    <row r="398" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B398" s="2">
         <v>1707</v>
       </c>
@@ -9309,7 +8703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="2:7">
+    <row r="399" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B399" s="2">
         <v>1707</v>
       </c>
@@ -9326,7 +8720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="2:8">
+    <row r="400" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B400" s="2">
         <v>1707</v>
       </c>
@@ -9346,7 +8740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="401" spans="2:7">
+    <row r="401" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B401" s="2">
         <v>1707</v>
       </c>
@@ -9363,7 +8757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="2:7">
+    <row r="402" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B402" s="2">
         <v>1707</v>
       </c>
@@ -9380,7 +8774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="2:7">
+    <row r="403" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B403" s="2">
         <v>1707</v>
       </c>
@@ -9397,7 +8791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="2:7">
+    <row r="404" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B404" s="2">
         <v>1707</v>
       </c>
@@ -9414,7 +8808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="2:7">
+    <row r="405" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B405" s="2">
         <v>1707</v>
       </c>
@@ -9431,7 +8825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="2:7">
+    <row r="406" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B406" s="2">
         <v>1707</v>
       </c>
@@ -9448,7 +8842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="2:7">
+    <row r="407" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B407" s="2">
         <v>1707</v>
       </c>
@@ -9465,7 +8859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="2:7">
+    <row r="408" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B408" s="2">
         <v>1707</v>
       </c>
@@ -9482,7 +8876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="409" spans="2:8">
+    <row r="409" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B409" s="2">
         <v>1707</v>
       </c>
@@ -9502,7 +8896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="410" spans="2:7">
+    <row r="410" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B410" s="2">
         <v>1707</v>
       </c>
@@ -9519,7 +8913,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="411" spans="2:7">
+    <row r="411" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B411" s="2">
         <v>1707</v>
       </c>
@@ -9536,7 +8930,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="412" spans="2:7">
+    <row r="412" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B412" s="2">
         <v>1707</v>
       </c>
@@ -9553,7 +8947,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="413" spans="2:7">
+    <row r="413" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B413" s="2">
         <v>1707</v>
       </c>
@@ -9570,7 +8964,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="414" spans="2:7">
+    <row r="414" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B414" s="2">
         <v>1707</v>
       </c>
@@ -9587,7 +8981,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="415" spans="2:7">
+    <row r="415" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B415" s="2">
         <v>1707</v>
       </c>
@@ -9604,7 +8998,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="416" spans="2:7">
+    <row r="416" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B416" s="2">
         <v>1707</v>
       </c>
@@ -9621,7 +9015,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="417" spans="2:7">
+    <row r="417" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B417" s="2">
         <v>1707</v>
       </c>
@@ -9638,7 +9032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="418" spans="2:7">
+    <row r="418" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B418" s="2">
         <v>1707</v>
       </c>
@@ -9655,7 +9049,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="419" spans="2:7">
+    <row r="419" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B419" s="2">
         <v>1707</v>
       </c>
@@ -9672,7 +9066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="420" spans="2:7">
+    <row r="420" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B420" s="2">
         <v>1707</v>
       </c>
@@ -9689,7 +9083,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="421" spans="2:8">
+    <row r="421" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B421" s="2">
         <v>1707</v>
       </c>
@@ -9709,7 +9103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="422" spans="2:7">
+    <row r="422" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B422" s="2">
         <v>1707</v>
       </c>
@@ -9726,7 +9120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="423" spans="2:7">
+    <row r="423" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B423" s="2">
         <v>1707</v>
       </c>
@@ -9743,7 +9137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="424" spans="2:7">
+    <row r="424" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B424" s="2">
         <v>1707</v>
       </c>
@@ -9760,7 +9154,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="425" spans="2:7">
+    <row r="425" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B425" s="2">
         <v>1707</v>
       </c>
@@ -9777,7 +9171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="426" spans="2:7">
+    <row r="426" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B426" s="2">
         <v>1707</v>
       </c>
@@ -9794,7 +9188,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="427" spans="2:7">
+    <row r="427" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B427" s="2">
         <v>1707</v>
       </c>
@@ -9811,7 +9205,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="428" spans="2:7">
+    <row r="428" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B428" s="2">
         <v>1707</v>
       </c>
@@ -9828,7 +9222,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="429" spans="2:7">
+    <row r="429" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B429" s="2">
         <v>1707</v>
       </c>
@@ -9845,7 +9239,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="430" spans="2:8">
+    <row r="430" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B430" s="2">
         <v>1707</v>
       </c>
@@ -9865,7 +9259,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="431" spans="2:7">
+    <row r="431" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B431" s="2">
         <v>1707</v>
       </c>
@@ -9882,7 +9276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="432" spans="2:7">
+    <row r="432" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B432" s="2">
         <v>1707</v>
       </c>
@@ -9899,7 +9293,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" spans="2:7">
+    <row r="433" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B433" s="2">
         <v>1707</v>
       </c>
@@ -9916,7 +9310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="2:7">
+    <row r="434" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B434" s="2">
         <v>1707</v>
       </c>
@@ -9933,7 +9327,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="435" spans="2:7">
+    <row r="435" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B435" s="2">
         <v>1707</v>
       </c>
@@ -9950,7 +9344,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="436" spans="2:7">
+    <row r="436" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B436" s="2">
         <v>1707</v>
       </c>
@@ -9967,7 +9361,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="437" spans="2:7">
+    <row r="437" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B437" s="2">
         <v>1707</v>
       </c>
@@ -9984,7 +9378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="438" spans="2:7">
+    <row r="438" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B438" s="2">
         <v>1707</v>
       </c>
@@ -10001,7 +9395,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="439" spans="2:8">
+    <row r="439" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B439" s="2">
         <v>1707</v>
       </c>
@@ -10021,7 +9415,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="440" spans="2:7">
+    <row r="440" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B440" s="2">
         <v>1707</v>
       </c>
@@ -10038,7 +9432,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="441" spans="2:7">
+    <row r="441" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B441" s="2">
         <v>1707</v>
       </c>
@@ -10055,7 +9449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="442" spans="2:7">
+    <row r="442" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B442" s="2">
         <v>1707</v>
       </c>
@@ -10072,7 +9466,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="443" spans="2:7">
+    <row r="443" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B443" s="2">
         <v>1707</v>
       </c>
@@ -10089,7 +9483,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="444" spans="2:7">
+    <row r="444" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B444" s="2">
         <v>1707</v>
       </c>
@@ -10106,7 +9500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="445" spans="2:7">
+    <row r="445" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B445" s="2">
         <v>1707</v>
       </c>
@@ -10123,7 +9517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="446" spans="2:7">
+    <row r="446" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B446" s="2">
         <v>1707</v>
       </c>
@@ -10140,7 +9534,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="447" spans="2:7">
+    <row r="447" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B447" s="2">
         <v>1707</v>
       </c>
@@ -10157,7 +9551,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="448" spans="2:7">
+    <row r="448" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B448" s="2">
         <v>1707</v>
       </c>
@@ -10174,7 +9568,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="449" spans="2:7">
+    <row r="449" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B449" s="2">
         <v>1708</v>
       </c>
@@ -10191,7 +9585,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="450" spans="2:7">
+    <row r="450" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B450" s="2">
         <v>1708</v>
       </c>
@@ -10208,7 +9602,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="451" spans="2:8">
+    <row r="451" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B451" s="2">
         <v>1708</v>
       </c>
@@ -10228,7 +9622,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="452" spans="2:7">
+    <row r="452" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B452" s="2">
         <v>1708</v>
       </c>
@@ -10245,7 +9639,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="453" spans="2:7">
+    <row r="453" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B453" s="2">
         <v>1708</v>
       </c>
@@ -10262,7 +9656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="454" spans="2:7">
+    <row r="454" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B454" s="2">
         <v>1708</v>
       </c>
@@ -10279,7 +9673,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="455" spans="2:7">
+    <row r="455" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B455" s="2">
         <v>1708</v>
       </c>
@@ -10296,7 +9690,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="456" spans="2:7">
+    <row r="456" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B456" s="2">
         <v>1708</v>
       </c>
@@ -10313,7 +9707,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="457" spans="2:7">
+    <row r="457" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B457" s="2">
         <v>1708</v>
       </c>
@@ -10330,7 +9724,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="458" spans="2:7">
+    <row r="458" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B458" s="2">
         <v>1708</v>
       </c>
@@ -10347,7 +9741,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="459" spans="2:7">
+    <row r="459" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B459" s="2">
         <v>1708</v>
       </c>
@@ -10365,23 +9759,22 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>101</v>
       </c>
@@ -10390,20 +9783,19 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>